--- a/海南省村界/WebMap/省长选举.xlsx
+++ b/海南省村界/WebMap/省长选举.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-113" yWindow="-113" windowWidth="32281" windowHeight="17531" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2010" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2010" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -957,16 +957,16 @@
         <v>583</v>
       </c>
       <c r="I13" t="n">
-        <v>28941</v>
+        <v>31847</v>
       </c>
       <c r="J13" t="n">
-        <v>57.94</v>
+        <v>63.76</v>
       </c>
       <c r="K13" t="n">
-        <v>21007</v>
+        <v>18101</v>
       </c>
       <c r="L13" t="n">
-        <v>42.06</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="14">
@@ -1125,16 +1125,16 @@
         <v>764</v>
       </c>
       <c r="I17" t="n">
-        <v>37084</v>
+        <v>40169</v>
       </c>
       <c r="J17" t="n">
-        <v>56.88</v>
+        <v>61.61</v>
       </c>
       <c r="K17" t="n">
-        <v>28116</v>
+        <v>25031</v>
       </c>
       <c r="L17" t="n">
-        <v>43.12</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="18">
@@ -1503,16 +1503,16 @@
         <v>4261</v>
       </c>
       <c r="I26" t="n">
-        <v>101436</v>
+        <v>106173</v>
       </c>
       <c r="J26" t="n">
-        <v>52.24</v>
+        <v>54.68</v>
       </c>
       <c r="K26" t="n">
-        <v>92720</v>
+        <v>87983</v>
       </c>
       <c r="L26" t="n">
-        <v>47.76</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="27">
@@ -1629,16 +1629,16 @@
         <v>313</v>
       </c>
       <c r="I29" t="n">
-        <v>5062</v>
+        <v>5822</v>
       </c>
       <c r="J29" t="n">
-        <v>35.14</v>
+        <v>40.41</v>
       </c>
       <c r="K29" t="n">
-        <v>9345</v>
+        <v>8585</v>
       </c>
       <c r="L29" t="n">
-        <v>64.86</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="30">
@@ -1671,16 +1671,16 @@
         <v>259</v>
       </c>
       <c r="I30" t="n">
-        <v>6102</v>
+        <v>6504</v>
       </c>
       <c r="J30" t="n">
-        <v>40.62</v>
+        <v>43.29</v>
       </c>
       <c r="K30" t="n">
-        <v>8920</v>
+        <v>8518</v>
       </c>
       <c r="L30" t="n">
-        <v>59.38</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="31">
@@ -1923,16 +1923,16 @@
         <v>1257</v>
       </c>
       <c r="I36" t="n">
-        <v>34131</v>
+        <v>35415</v>
       </c>
       <c r="J36" t="n">
-        <v>58.44</v>
+        <v>60.63</v>
       </c>
       <c r="K36" t="n">
-        <v>24276</v>
+        <v>22992</v>
       </c>
       <c r="L36" t="n">
-        <v>41.56</v>
+        <v>39.37</v>
       </c>
     </row>
     <row r="37">
@@ -2343,16 +2343,16 @@
         <v>1312</v>
       </c>
       <c r="I46" t="n">
-        <v>26382</v>
+        <v>29500</v>
       </c>
       <c r="J46" t="n">
-        <v>50.75</v>
+        <v>56.75</v>
       </c>
       <c r="K46" t="n">
-        <v>25601</v>
+        <v>22483</v>
       </c>
       <c r="L46" t="n">
-        <v>49.25</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="47">
@@ -2595,16 +2595,16 @@
         <v>316</v>
       </c>
       <c r="I52" t="n">
-        <v>10162</v>
+        <v>10837</v>
       </c>
       <c r="J52" t="n">
-        <v>52.6</v>
+        <v>56.1</v>
       </c>
       <c r="K52" t="n">
-        <v>9156</v>
+        <v>8481</v>
       </c>
       <c r="L52" t="n">
-        <v>47.4</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="53">
@@ -2721,16 +2721,16 @@
         <v>478</v>
       </c>
       <c r="I55" t="n">
-        <v>12227</v>
+        <v>12650</v>
       </c>
       <c r="J55" t="n">
-        <v>52.12</v>
+        <v>53.92</v>
       </c>
       <c r="K55" t="n">
-        <v>11233</v>
+        <v>10810</v>
       </c>
       <c r="L55" t="n">
-        <v>47.88</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="56">
@@ -2763,16 +2763,16 @@
         <v>525</v>
       </c>
       <c r="I56" t="n">
-        <v>18473</v>
+        <v>19153</v>
       </c>
       <c r="J56" t="n">
-        <v>65.34</v>
+        <v>67.75</v>
       </c>
       <c r="K56" t="n">
-        <v>9799</v>
+        <v>9119</v>
       </c>
       <c r="L56" t="n">
-        <v>34.66</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="57">
@@ -2973,16 +2973,16 @@
         <v>180</v>
       </c>
       <c r="I61" t="n">
-        <v>6600</v>
+        <v>7227</v>
       </c>
       <c r="J61" t="n">
-        <v>56.01</v>
+        <v>61.33</v>
       </c>
       <c r="K61" t="n">
-        <v>5184</v>
+        <v>4557</v>
       </c>
       <c r="L61" t="n">
-        <v>43.99</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="62">
@@ -3015,16 +3015,16 @@
         <v>795</v>
       </c>
       <c r="I62" t="n">
-        <v>18455</v>
+        <v>19510</v>
       </c>
       <c r="J62" t="n">
-        <v>47.14</v>
+        <v>49.84</v>
       </c>
       <c r="K62" t="n">
-        <v>20692</v>
+        <v>19637</v>
       </c>
       <c r="L62" t="n">
-        <v>52.86</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="63">
@@ -3057,16 +3057,16 @@
         <v>952</v>
       </c>
       <c r="I63" t="n">
-        <v>15888</v>
+        <v>19052</v>
       </c>
       <c r="J63" t="n">
-        <v>46.05</v>
+        <v>55.23</v>
       </c>
       <c r="K63" t="n">
-        <v>18610</v>
+        <v>15446</v>
       </c>
       <c r="L63" t="n">
-        <v>53.95</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="64">
@@ -3393,16 +3393,16 @@
         <v>866</v>
       </c>
       <c r="I71" t="n">
-        <v>20852</v>
+        <v>22208</v>
       </c>
       <c r="J71" t="n">
-        <v>58.32</v>
+        <v>62.11</v>
       </c>
       <c r="K71" t="n">
-        <v>14904</v>
+        <v>13548</v>
       </c>
       <c r="L71" t="n">
-        <v>41.68</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="72">
@@ -3435,13 +3435,13 @@
         <v>95</v>
       </c>
       <c r="I72" t="n">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="J72" t="n">
         <v>67.25</v>
       </c>
       <c r="K72" t="n">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="L72" t="n">
         <v>32.75</v>
@@ -3603,16 +3603,16 @@
         <v>110</v>
       </c>
       <c r="I76" t="n">
-        <v>4977</v>
+        <v>6496</v>
       </c>
       <c r="J76" t="n">
-        <v>62.26</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>3017</v>
+        <v>1498</v>
       </c>
       <c r="L76" t="n">
-        <v>37.74</v>
+        <v>18.74</v>
       </c>
     </row>
     <row r="77">
@@ -3645,16 +3645,16 @@
         <v>33</v>
       </c>
       <c r="I77" t="n">
-        <v>1051</v>
+        <v>1172</v>
       </c>
       <c r="J77" t="n">
-        <v>69.17</v>
+        <v>77.17</v>
       </c>
       <c r="K77" t="n">
-        <v>468</v>
+        <v>347</v>
       </c>
       <c r="L77" t="n">
-        <v>30.83</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="78">
@@ -3687,16 +3687,16 @@
         <v>74</v>
       </c>
       <c r="I78" t="n">
-        <v>3313</v>
+        <v>3612</v>
       </c>
       <c r="J78" t="n">
-        <v>66.54000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>1666</v>
+        <v>1367</v>
       </c>
       <c r="L78" t="n">
-        <v>33.46</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="79">
@@ -3813,16 +3813,16 @@
         <v>259</v>
       </c>
       <c r="I81" t="n">
-        <v>5102</v>
+        <v>6062</v>
       </c>
       <c r="J81" t="n">
-        <v>43.1</v>
+        <v>51.21</v>
       </c>
       <c r="K81" t="n">
-        <v>6735</v>
+        <v>5775</v>
       </c>
       <c r="L81" t="n">
-        <v>56.9</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="82">
@@ -4107,16 +4107,16 @@
         <v>578</v>
       </c>
       <c r="I88" t="n">
-        <v>11337</v>
+        <v>11869</v>
       </c>
       <c r="J88" t="n">
-        <v>51.12</v>
+        <v>53.51</v>
       </c>
       <c r="K88" t="n">
-        <v>10842</v>
+        <v>10310</v>
       </c>
       <c r="L88" t="n">
-        <v>48.88</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="89">
@@ -4191,16 +4191,16 @@
         <v>393</v>
       </c>
       <c r="I90" t="n">
-        <v>7856</v>
+        <v>8456</v>
       </c>
       <c r="J90" t="n">
-        <v>47.42</v>
+        <v>51.04</v>
       </c>
       <c r="K90" t="n">
-        <v>8712</v>
+        <v>8112</v>
       </c>
       <c r="L90" t="n">
-        <v>52.58</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="91">
@@ -4737,16 +4737,16 @@
         <v>3743</v>
       </c>
       <c r="I103" t="n">
-        <v>74281</v>
+        <v>76655</v>
       </c>
       <c r="J103" t="n">
-        <v>44.14</v>
+        <v>45.55</v>
       </c>
       <c r="K103" t="n">
-        <v>94021</v>
+        <v>91647</v>
       </c>
       <c r="L103" t="n">
-        <v>55.86</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="104">
@@ -4989,16 +4989,16 @@
         <v>1114</v>
       </c>
       <c r="I109" t="n">
-        <v>20557</v>
+        <v>21073</v>
       </c>
       <c r="J109" t="n">
-        <v>50.55</v>
+        <v>51.82</v>
       </c>
       <c r="K109" t="n">
-        <v>20112</v>
+        <v>19596</v>
       </c>
       <c r="L109" t="n">
-        <v>49.45</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="110">
@@ -5535,16 +5535,16 @@
         <v>455</v>
       </c>
       <c r="I122" t="n">
-        <v>9048</v>
+        <v>7731</v>
       </c>
       <c r="J122" t="n">
-        <v>42.24</v>
+        <v>36.09</v>
       </c>
       <c r="K122" t="n">
-        <v>12370</v>
+        <v>13687</v>
       </c>
       <c r="L122" t="n">
-        <v>57.76</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="123">
@@ -6855,16 +6855,16 @@
         <v>1071</v>
       </c>
       <c r="I154" t="n">
-        <v>34446</v>
+        <v>35250</v>
       </c>
       <c r="J154" t="n">
-        <v>56.66</v>
+        <v>57.98</v>
       </c>
       <c r="K154" t="n">
-        <v>26348</v>
+        <v>25544</v>
       </c>
       <c r="L154" t="n">
-        <v>43.34</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="155">
@@ -7401,16 +7401,16 @@
         <v>655</v>
       </c>
       <c r="I167" t="n">
-        <v>18229</v>
+        <v>19967</v>
       </c>
       <c r="J167" t="n">
-        <v>58.45</v>
+        <v>64.02</v>
       </c>
       <c r="K167" t="n">
-        <v>12959</v>
+        <v>11221</v>
       </c>
       <c r="L167" t="n">
-        <v>41.55</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="168">
@@ -7485,16 +7485,16 @@
         <v>454</v>
       </c>
       <c r="I169" t="n">
-        <v>16238</v>
+        <v>17314</v>
       </c>
       <c r="J169" t="n">
-        <v>51.06</v>
+        <v>54.44</v>
       </c>
       <c r="K169" t="n">
-        <v>15566</v>
+        <v>14490</v>
       </c>
       <c r="L169" t="n">
-        <v>48.94</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="170">
@@ -7527,16 +7527,16 @@
         <v>180</v>
       </c>
       <c r="I170" t="n">
-        <v>2793</v>
+        <v>3634</v>
       </c>
       <c r="J170" t="n">
-        <v>35.35</v>
+        <v>46.01</v>
       </c>
       <c r="K170" t="n">
-        <v>5106</v>
+        <v>4265</v>
       </c>
       <c r="L170" t="n">
-        <v>64.65000000000001</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="171">
@@ -7569,16 +7569,16 @@
         <v>279</v>
       </c>
       <c r="I171" t="n">
-        <v>5555</v>
+        <v>6019</v>
       </c>
       <c r="J171" t="n">
-        <v>37.58</v>
+        <v>40.72</v>
       </c>
       <c r="K171" t="n">
-        <v>9227</v>
+        <v>8763</v>
       </c>
       <c r="L171" t="n">
-        <v>62.42</v>
+        <v>59.28</v>
       </c>
     </row>
     <row r="172">
@@ -7653,16 +7653,16 @@
         <v>952</v>
       </c>
       <c r="I173" t="n">
-        <v>36818</v>
+        <v>38790</v>
       </c>
       <c r="J173" t="n">
-        <v>56.94</v>
+        <v>59.99</v>
       </c>
       <c r="K173" t="n">
-        <v>27838</v>
+        <v>25866</v>
       </c>
       <c r="L173" t="n">
-        <v>43.06</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="174">
@@ -8031,13 +8031,13 @@
         <v>211</v>
       </c>
       <c r="I182" t="n">
-        <v>5188</v>
+        <v>5187</v>
       </c>
       <c r="J182" t="n">
         <v>61.64</v>
       </c>
       <c r="K182" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="L182" t="n">
         <v>38.36</v>
@@ -8115,16 +8115,16 @@
         <v>87</v>
       </c>
       <c r="I184" t="n">
-        <v>4229</v>
+        <v>4924</v>
       </c>
       <c r="J184" t="n">
-        <v>66.95999999999999</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K184" t="n">
-        <v>2087</v>
+        <v>1392</v>
       </c>
       <c r="L184" t="n">
-        <v>33.04</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="185">
@@ -8157,16 +8157,16 @@
         <v>46</v>
       </c>
       <c r="I185" t="n">
-        <v>2371</v>
+        <v>2790</v>
       </c>
       <c r="J185" t="n">
-        <v>62.17</v>
+        <v>73.17</v>
       </c>
       <c r="K185" t="n">
-        <v>1442</v>
+        <v>1023</v>
       </c>
       <c r="L185" t="n">
-        <v>37.83</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="186">
@@ -8199,16 +8199,16 @@
         <v>132</v>
       </c>
       <c r="I186" t="n">
-        <v>3241</v>
+        <v>3739</v>
       </c>
       <c r="J186" t="n">
-        <v>65.01000000000001</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="K186" t="n">
-        <v>1744</v>
+        <v>1246</v>
       </c>
       <c r="L186" t="n">
-        <v>34.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="187">
@@ -8241,16 +8241,16 @@
         <v>118</v>
       </c>
       <c r="I187" t="n">
-        <v>9386</v>
+        <v>11065</v>
       </c>
       <c r="J187" t="n">
-        <v>69.33</v>
+        <v>81.73</v>
       </c>
       <c r="K187" t="n">
-        <v>4152</v>
+        <v>2473</v>
       </c>
       <c r="L187" t="n">
-        <v>30.67</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="188">
@@ -8367,16 +8367,16 @@
         <v>985</v>
       </c>
       <c r="I190" t="n">
-        <v>21322</v>
+        <v>21421</v>
       </c>
       <c r="J190" t="n">
-        <v>53.48</v>
+        <v>53.73</v>
       </c>
       <c r="K190" t="n">
-        <v>18548</v>
+        <v>18449</v>
       </c>
       <c r="L190" t="n">
-        <v>46.52</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="191">
@@ -8451,16 +8451,16 @@
         <v>368</v>
       </c>
       <c r="I192" t="n">
-        <v>7836</v>
+        <v>9602</v>
       </c>
       <c r="J192" t="n">
-        <v>42.84</v>
+        <v>52.49</v>
       </c>
       <c r="K192" t="n">
-        <v>10456</v>
+        <v>8690</v>
       </c>
       <c r="L192" t="n">
-        <v>57.16</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="193">
@@ -8619,16 +8619,16 @@
         <v>320</v>
       </c>
       <c r="I196" t="n">
-        <v>5538</v>
+        <v>6517</v>
       </c>
       <c r="J196" t="n">
-        <v>39.6</v>
+        <v>46.6</v>
       </c>
       <c r="K196" t="n">
-        <v>8448</v>
+        <v>7469</v>
       </c>
       <c r="L196" t="n">
-        <v>60.4</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="197">
@@ -9375,16 +9375,16 @@
         <v>40</v>
       </c>
       <c r="I214" t="n">
-        <v>837</v>
+        <v>919</v>
       </c>
       <c r="J214" t="n">
-        <v>40.09</v>
+        <v>43.99</v>
       </c>
       <c r="K214" t="n">
-        <v>1251</v>
+        <v>1169</v>
       </c>
       <c r="L214" t="n">
-        <v>59.91</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="215">
@@ -9921,16 +9921,16 @@
         <v>325</v>
       </c>
       <c r="I227" t="n">
-        <v>6550</v>
+        <v>7343</v>
       </c>
       <c r="J227" t="n">
-        <v>37.89</v>
+        <v>42.47</v>
       </c>
       <c r="K227" t="n">
-        <v>10738</v>
+        <v>9945</v>
       </c>
       <c r="L227" t="n">
-        <v>62.11</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="228">
@@ -11517,13 +11517,13 @@
         <v>849</v>
       </c>
       <c r="I265" t="n">
-        <v>23007</v>
+        <v>23006</v>
       </c>
       <c r="J265" t="n">
         <v>54.34</v>
       </c>
       <c r="K265" t="n">
-        <v>19333</v>
+        <v>19334</v>
       </c>
       <c r="L265" t="n">
         <v>45.66</v>
@@ -11601,13 +11601,13 @@
         <v>238</v>
       </c>
       <c r="I267" t="n">
-        <v>5357</v>
+        <v>5356</v>
       </c>
       <c r="J267" t="n">
         <v>54.93</v>
       </c>
       <c r="K267" t="n">
-        <v>4395</v>
+        <v>4396</v>
       </c>
       <c r="L267" t="n">
         <v>45.07</v>
@@ -11811,13 +11811,13 @@
         <v>254</v>
       </c>
       <c r="I272" t="n">
-        <v>7323</v>
+        <v>7322</v>
       </c>
       <c r="J272" t="n">
         <v>53.01</v>
       </c>
       <c r="K272" t="n">
-        <v>6490</v>
+        <v>6491</v>
       </c>
       <c r="L272" t="n">
         <v>46.99</v>
@@ -11895,13 +11895,13 @@
         <v>154</v>
       </c>
       <c r="I274" t="n">
-        <v>8846</v>
+        <v>8845</v>
       </c>
       <c r="J274" t="n">
         <v>74.87</v>
       </c>
       <c r="K274" t="n">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="L274" t="n">
         <v>25.13</v>
@@ -12021,16 +12021,16 @@
         <v>1051</v>
       </c>
       <c r="I277" t="n">
-        <v>28602</v>
+        <v>30791</v>
       </c>
       <c r="J277" t="n">
-        <v>55.66</v>
+        <v>59.92</v>
       </c>
       <c r="K277" t="n">
-        <v>22787</v>
+        <v>20598</v>
       </c>
       <c r="L277" t="n">
-        <v>44.34</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="278">
@@ -12063,16 +12063,16 @@
         <v>284</v>
       </c>
       <c r="I278" t="n">
-        <v>12924</v>
+        <v>13410</v>
       </c>
       <c r="J278" t="n">
-        <v>58.71</v>
+        <v>60.92</v>
       </c>
       <c r="K278" t="n">
-        <v>9088</v>
+        <v>8602</v>
       </c>
       <c r="L278" t="n">
-        <v>41.29</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="279">
@@ -12105,16 +12105,16 @@
         <v>223</v>
       </c>
       <c r="I279" t="n">
-        <v>6190</v>
+        <v>6386</v>
       </c>
       <c r="J279" t="n">
-        <v>49.53</v>
+        <v>51.1</v>
       </c>
       <c r="K279" t="n">
-        <v>6308</v>
+        <v>6112</v>
       </c>
       <c r="L279" t="n">
-        <v>50.47</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="280">
@@ -12189,13 +12189,13 @@
         <v>654</v>
       </c>
       <c r="I281" t="n">
-        <v>22547</v>
+        <v>22550</v>
       </c>
       <c r="J281" t="n">
         <v>55.86</v>
       </c>
       <c r="K281" t="n">
-        <v>17818</v>
+        <v>17815</v>
       </c>
       <c r="L281" t="n">
         <v>44.14</v>
@@ -12231,13 +12231,13 @@
         <v>720</v>
       </c>
       <c r="I282" t="n">
-        <v>16924</v>
+        <v>16926</v>
       </c>
       <c r="J282" t="n">
         <v>60.61</v>
       </c>
       <c r="K282" t="n">
-        <v>11000</v>
+        <v>10998</v>
       </c>
       <c r="L282" t="n">
         <v>39.39</v>
@@ -12273,16 +12273,16 @@
         <v>53</v>
       </c>
       <c r="I283" t="n">
-        <v>1474</v>
+        <v>1686</v>
       </c>
       <c r="J283" t="n">
-        <v>69.38</v>
+        <v>79.38</v>
       </c>
       <c r="K283" t="n">
-        <v>650</v>
+        <v>438</v>
       </c>
       <c r="L283" t="n">
-        <v>30.62</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="284">
@@ -12357,13 +12357,13 @@
         <v>307</v>
       </c>
       <c r="I285" t="n">
-        <v>14352</v>
+        <v>14351</v>
       </c>
       <c r="J285" t="n">
         <v>72.16</v>
       </c>
       <c r="K285" t="n">
-        <v>5537</v>
+        <v>5538</v>
       </c>
       <c r="L285" t="n">
         <v>27.84</v>
@@ -12483,13 +12483,13 @@
         <v>169</v>
       </c>
       <c r="I288" t="n">
-        <v>5054</v>
+        <v>5055</v>
       </c>
       <c r="J288" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="K288" t="n">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="L288" t="n">
         <v>32.51</v>
@@ -12525,13 +12525,13 @@
         <v>196</v>
       </c>
       <c r="I289" t="n">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="J289" t="n">
         <v>70.16</v>
       </c>
       <c r="K289" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="L289" t="n">
         <v>29.84</v>
@@ -12609,16 +12609,16 @@
         <v>191</v>
       </c>
       <c r="I291" t="n">
-        <v>7009</v>
+        <v>7350</v>
       </c>
       <c r="J291" t="n">
-        <v>62.8</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="K291" t="n">
-        <v>4152</v>
+        <v>3811</v>
       </c>
       <c r="L291" t="n">
-        <v>37.2</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="292">
@@ -12651,16 +12651,16 @@
         <v>305</v>
       </c>
       <c r="I292" t="n">
-        <v>8023</v>
+        <v>9391</v>
       </c>
       <c r="J292" t="n">
-        <v>58.71</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="K292" t="n">
-        <v>5644</v>
+        <v>4276</v>
       </c>
       <c r="L292" t="n">
-        <v>41.29</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="293">
@@ -12693,13 +12693,13 @@
         <v>1069</v>
       </c>
       <c r="I293" t="n">
-        <v>28807</v>
+        <v>28811</v>
       </c>
       <c r="J293" t="n">
         <v>62.56</v>
       </c>
       <c r="K293" t="n">
-        <v>17244</v>
+        <v>17240</v>
       </c>
       <c r="L293" t="n">
         <v>37.44</v>
@@ -12861,13 +12861,13 @@
         <v>290</v>
       </c>
       <c r="I297" t="n">
-        <v>12058</v>
+        <v>12060</v>
       </c>
       <c r="J297" t="n">
         <v>72.75</v>
       </c>
       <c r="K297" t="n">
-        <v>4518</v>
+        <v>4516</v>
       </c>
       <c r="L297" t="n">
         <v>27.25</v>
@@ -12903,13 +12903,13 @@
         <v>182</v>
       </c>
       <c r="I298" t="n">
-        <v>5960</v>
+        <v>5959</v>
       </c>
       <c r="J298" t="n">
         <v>65.53</v>
       </c>
       <c r="K298" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="L298" t="n">
         <v>34.47</v>
@@ -13113,13 +13113,13 @@
         <v>406</v>
       </c>
       <c r="I303" t="n">
-        <v>8799</v>
+        <v>8800</v>
       </c>
       <c r="J303" t="n">
         <v>55.35</v>
       </c>
       <c r="K303" t="n">
-        <v>7099</v>
+        <v>7098</v>
       </c>
       <c r="L303" t="n">
         <v>44.65</v>
@@ -13155,13 +13155,13 @@
         <v>420</v>
       </c>
       <c r="I304" t="n">
-        <v>13954</v>
+        <v>13956</v>
       </c>
       <c r="J304" t="n">
         <v>61.08</v>
       </c>
       <c r="K304" t="n">
-        <v>8893</v>
+        <v>8891</v>
       </c>
       <c r="L304" t="n">
         <v>38.92</v>
@@ -13239,13 +13239,13 @@
         <v>243</v>
       </c>
       <c r="I306" t="n">
-        <v>7278</v>
+        <v>7277</v>
       </c>
       <c r="J306" t="n">
         <v>73.44</v>
       </c>
       <c r="K306" t="n">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="L306" t="n">
         <v>26.56</v>
@@ -13281,13 +13281,13 @@
         <v>174</v>
       </c>
       <c r="I307" t="n">
-        <v>7041</v>
+        <v>7040</v>
       </c>
       <c r="J307" t="n">
         <v>71.25</v>
       </c>
       <c r="K307" t="n">
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="L307" t="n">
         <v>28.75</v>
@@ -13323,16 +13323,16 @@
         <v>57</v>
       </c>
       <c r="I308" t="n">
-        <v>1708</v>
+        <v>1968</v>
       </c>
       <c r="J308" t="n">
-        <v>57.62</v>
+        <v>66.38</v>
       </c>
       <c r="K308" t="n">
-        <v>1257</v>
+        <v>997</v>
       </c>
       <c r="L308" t="n">
-        <v>42.38</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="309">
@@ -13449,16 +13449,16 @@
         <v>136</v>
       </c>
       <c r="I311" t="n">
-        <v>5185</v>
+        <v>5944</v>
       </c>
       <c r="J311" t="n">
-        <v>68.34</v>
+        <v>78.34</v>
       </c>
       <c r="K311" t="n">
-        <v>2402</v>
+        <v>1643</v>
       </c>
       <c r="L311" t="n">
-        <v>31.66</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="312">
@@ -13491,16 +13491,16 @@
         <v>43</v>
       </c>
       <c r="I312" t="n">
-        <v>1582</v>
+        <v>1692</v>
       </c>
       <c r="J312" t="n">
-        <v>57.91</v>
+        <v>61.97</v>
       </c>
       <c r="K312" t="n">
-        <v>1149</v>
+        <v>1039</v>
       </c>
       <c r="L312" t="n">
-        <v>42.09</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="313">
@@ -13827,16 +13827,16 @@
         <v>102</v>
       </c>
       <c r="I320" t="n">
-        <v>3131</v>
+        <v>3749</v>
       </c>
       <c r="J320" t="n">
-        <v>66.73999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K320" t="n">
-        <v>1561</v>
+        <v>943</v>
       </c>
       <c r="L320" t="n">
-        <v>33.26</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="321">
